--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25916,7 +25916,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:01)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:06)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:27)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:29)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:29)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:39)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:39)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:40)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:40)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:49)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:49)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:50)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 17:50)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 18:05)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 18:05)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 18:09)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (30/09/2026 18:09)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 08:37)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 08:37)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 08:40)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 08:40)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 09:15)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -25892,7 +25892,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 09:15)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (01/10/2026 09:44)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/docs/OS_exemplo_cam21.xlsx
+++ b/docs/OS_exemplo_cam21.xlsx
@@ -26447,7 +26447,7 @@
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (07/10/2026 11:56)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8Controle de CFTV — Ordem de Serviço (07/10/2026 12:15)&amp;R&amp;8Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>